--- a/artfynd/A 36471-2022 artfynd.xlsx
+++ b/artfynd/A 36471-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36471-2022 artfynd.xlsx
+++ b/artfynd/A 36471-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75085767</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689934.9090662554</v>
+        <v>689935</v>
       </c>
       <c r="R2" t="n">
-        <v>6658962.209412632</v>
+        <v>6658962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2002-06-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86972484</v>
+        <v>86972480</v>
       </c>
       <c r="B3" t="n">
-        <v>5219</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102147</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -862,7 +842,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -876,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689947.0849263561</v>
+        <v>689947</v>
       </c>
       <c r="R3" t="n">
-        <v>6658949.818275782</v>
+        <v>6658950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,19 +889,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -938,21 +908,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -969,15 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86972480</v>
+        <v>86972484</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,26 +935,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>102147</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schrank, 1781)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1020,7 +970,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1034,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689947.0849263561</v>
+        <v>689947</v>
       </c>
       <c r="R4" t="n">
-        <v>6658949.818275782</v>
+        <v>6658950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1067,19 +1017,9 @@
           <t>2020-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1096,6 +1036,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
